--- a/public/crawlability-spdata-september-2026.xlsx
+++ b/public/crawlability-spdata-september-2026.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של spdata ב-SE Ranking (הסריקה האחרונה: 2026-07-21).</t>
+          <t>להריץ מחדש את ה-Website Audit של spdata ב-SE Ranking (הסריקה האחרונה: 2026-07-21); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. שגיאת כתיב בקישור (ויזואליציה במקום ויזואליזציה); העמוד קיים בכתובת היעד.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). שגיאת כתיב בקישור (ויזואליציה במקום ויזואליזציה); העמוד קיים בכתובת היעד.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). מזהה עמוד שנמחק. להסיר את הקישור.</t>
+          <t>מזהה עמוד שנמחק. להסיר את הקישור.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>

--- a/public/crawlability-spdata-september-2026.xlsx
+++ b/public/crawlability-spdata-september-2026.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,11 +56,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -517,7 +509,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 2 כתובות (הבולטת: https://www.spdata.co.il/ויזואליציה-ודשבורדים-אינטראקטיביים/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://www.spdata.co.il/?page_id=378, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -525,14 +517,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://spdata.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://www.spdata.co.il/ויזואליציה-ודשבורדים-אינטראקטיביים/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -540,12 +532,27 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://spdata.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>להריץ מחדש את ה-Website Audit של spdata ב-SE Ranking (הסריקה האחרונה: 2026-07-21); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
@@ -562,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -636,7 +643,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ויזואליציה-ודשבורדים-אינטראקטיביים/</t>
         </is>
@@ -656,7 +663,7 @@
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/פתרונות-אנליטיקה-בענן-קליק-סנס/</t>
         </is>
@@ -671,55 +678,12 @@
           <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). שגיאת כתיב בקישור (ויזואליציה במקום ויזואליזציה); העמוד קיים בכתובת היעד.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ויזואליזציה-ודשבורדים-אינטראקטיביים/</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.spdata.co.il/?page_id=378</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.spdata.co.il/אקדמיה/</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>מזהה עמוד שנמחק. להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -810,7 +774,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>https://spdata.co.il/</t>
         </is>
@@ -823,7 +787,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/</t>
         </is>
@@ -834,7 +798,7 @@
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/תנאי-שימוש/</t>
         </is>
@@ -849,12 +813,12 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -931,7 +895,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/sitemap_index.xml</t>
         </is>
@@ -985,7 +949,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/sitemap_index.xml</t>
         </is>
@@ -1007,7 +971,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/post-sitemap.xml</t>
         </is>
@@ -1029,7 +993,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/page-sitemap.xml</t>
         </is>
@@ -1051,7 +1015,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/category-sitemap.xml</t>
         </is>
@@ -1073,7 +1037,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/sitemap.xml</t>
         </is>
@@ -1095,7 +1059,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/wp-sitemap.xml</t>
         </is>
@@ -1134,7 +1098,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/</t>
         </is>
@@ -1144,7 +1108,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ (0 הפניות)</t>
         </is>
@@ -1156,7 +1120,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>http://www.spdata.co.il/</t>
         </is>
@@ -1166,7 +1130,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ (1 הפניות)</t>
         </is>
@@ -1178,7 +1142,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>https://spdata.co.il/</t>
         </is>
@@ -1188,7 +1152,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ (1 הפניות)</t>
         </is>
@@ -1200,7 +1164,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>http://spdata.co.il/</t>
         </is>
@@ -1210,7 +1174,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/ (2 הפניות)</t>
         </is>
@@ -1263,7 +1227,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>https://www.spdata.co.il/</t>
         </is>
@@ -1359,7 +1323,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://odoo.spdata.co.il/</t>
         </is>

--- a/public/crawlability-spdata-september-2026.xlsx
+++ b/public/crawlability-spdata-september-2026.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://www.spdata.co.il/?page_id=378, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת; הבולטת https://www.spdata.co.il/?page_id=378 (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://www.spdata.co.il/ויזואליציה-ודשבורדים-אינטראקטיביים/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://www.spdata.co.il/ויזואליציה-ודשבורדים-אינטראקטיביים/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://spdata.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת https://spdata.co.il/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של spdata ב-SE Ranking (הסריקה האחרונה: 2026-07-21); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של spdata ב-SE Ranking; הסריקה האחרונה: 2026-07-21.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). שגיאת כתיב בקישור (ויזואליציה במקום ויזואליזציה); העמוד קיים בכתובת היעד.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). שגיאת כתיב בקישור (ויזואליציה במקום ויזואליזציה); העמוד קיים בכתובת היעד.</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">

--- a/public/crawlability-spdata-september-2026.xlsx
+++ b/public/crawlability-spdata-september-2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>odoo.spdata.co.il: אתר Odoo עם תוכן ברירת מחדל (My Website), 7 כתובות באינדקס גוגל. להגדיר noindex ו-Disallow: / או להסיר את האתר הציבורי של המודול.</t>
+          <t>odoo.spdata.co.il: אתר Odoo עם תוכן ברירת מחדל (My Website), 7 כתובות באינדקס גוגל. להגדיר X-Robots-Tag: noindex (לא Disallow, כדי שהכתובות שכבר באינדקס יוסרו) או להסיר את האתר הציבורי של המודול.</t>
         </is>
       </c>
     </row>
@@ -540,21 +540,6 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת https://spdata.co.il/ (קישור נכנס אחד).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של spdata ב-SE Ranking; הסריקה האחרונה: 2026-07-21.</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1325,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>אתר Odoo עם תוכן ברירת מחדל (My Website), 7 כתובות באינדקס גוגל. להגדיר noindex ו-Disallow: / או להסיר את האתר הציבורי של המודול.</t>
+          <t>אתר Odoo עם תוכן ברירת מחדל (My Website), 7 כתובות באינדקס גוגל. להגדיר X-Robots-Tag: noindex (לא Disallow, כדי שהכתובות שכבר באינדקס יוסרו) או להסיר את האתר הציבורי של המודול.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
